--- a/templates/fidelity_transactions_template.xlsx
+++ b/templates/fidelity_transactions_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The importer reads YOU BOUGHT, YOU SOLD, DIVIDEND RECEIVED, and REINVESTMENT rows.</t>
+          <t>The importer reads YOU BOUGHT, YOU SOLD, REINVESTMENT, DIVIDEND RECEIVED, LONG-TERM/SHORT-TERM CAP GAIN, and RETURN OF CAPITAL rows. Same-day distribution lines are summed into one payment. Other dated rows (ELECTRONIC FUNDS TRANSFER, CONTRIBUTION, FOREIGN TAX WITHHELD, INTEREST, FEES, TRANSFER OF ASSETS) are kept as account activity.</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Required for trades and dividends</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Invalid or blank symbols are skipped.</t>
+          <t>Trades and dividends need a valid symbol. Cash rows such as deposits and withdrawals usually have none and are still kept as account activity.</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Imported for dividends</t>
+          <t>Imported for dividends and cash activity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Positive amounts become cash DIVIDEND history entries.</t>
+          <t>Positive amounts become cash DIVIDEND history entries. Deposits, withdrawals, and transfers keep their sign, which tells money in from money out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Account Alpha</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Export everything</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Export all activity types for the full date range. The Dashboard's Account Alpha needs every deposit and withdrawal; a file filtered to trades or dividends only cannot supply them.</t>
         </is>
       </c>
     </row>
